--- a/data/trans_camb/P19C07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,07</t>
+          <t>-2,31; 2,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,14</t>
+          <t>-4,05; 0,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,08</t>
+          <t>-1,69; 3,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,68</t>
+          <t>0,74; 7,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,5</t>
+          <t>-0,55; 4,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,2</t>
+          <t>1,62; 7,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,37</t>
+          <t>-0,32; 4,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,49</t>
+          <t>-1,78; 1,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,29</t>
+          <t>0,83; 4,29</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 174,75</t>
+          <t>-57,21; 157,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-90,19; 37,05</t>
+          <t>-88,77; 32,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,55; 168,45</t>
+          <t>-39,27; 214,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 1383,68</t>
+          <t>-5,96; 1170,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,41; 861,91</t>
+          <t>-46,7; 853,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,14; 1796,83</t>
+          <t>43,83; 1503,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 281,84</t>
+          <t>-14,14; 250,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 100,3</t>
+          <t>-57,05; 110,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 271,13</t>
+          <t>17,46; 269,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,06</t>
+          <t>-4,69; -0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,63</t>
+          <t>-3,05; 2,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,25</t>
+          <t>-3,61; 2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -0,13</t>
+          <t>-5,26; -0,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,03</t>
+          <t>-4,51; 1,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,7</t>
+          <t>-3,51; 2,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -0,87</t>
+          <t>-4,53; -0,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,18</t>
+          <t>-2,99; 1,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,45</t>
+          <t>-2,51; 1,64</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-90,36; 11,08</t>
+          <t>-90,26; 5,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 136,99</t>
+          <t>-62,49; 156,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,2; 137,09</t>
+          <t>-65,49; 108,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,88; 17,31</t>
+          <t>-85,81; 2,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 40,41</t>
+          <t>-70,76; 64,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,09; 96,24</t>
+          <t>-54,92; 88,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-82,16; -23,03</t>
+          <t>-83,71; -22,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 40,01</t>
+          <t>-58,97; 40,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 45,9</t>
+          <t>-46,1; 58,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,41</t>
+          <t>-3,54; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,14</t>
+          <t>-3,22; 2,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 0,75</t>
+          <t>-4,86; 0,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,74</t>
+          <t>-2,87; 3,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,04</t>
+          <t>-2,51; 6,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 4,01</t>
+          <t>-3,08; 3,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,28</t>
+          <t>-2,66; 1,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,86</t>
+          <t>-2,59; 1,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,82</t>
+          <t>-3,85; 0,87</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,51; 51,63</t>
+          <t>-63,32; 39,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,94; 80,61</t>
+          <t>-61,69; 75,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,05; 20,15</t>
+          <t>-86,46; 25,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,97; —</t>
+          <t>-73,23; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,99; —</t>
+          <t>-82,39; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,64; —</t>
+          <t>-71,21; 580,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 50,79</t>
+          <t>-55,58; 55,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 70,44</t>
+          <t>-54,73; 72,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,14; 31,41</t>
+          <t>-76,47; 25,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,45</t>
+          <t>-1,87; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,08</t>
+          <t>-2,13; 1,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,36</t>
+          <t>-1,82; 1,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,31</t>
+          <t>-2,0; 2,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,81</t>
+          <t>-1,62; 2,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,28</t>
+          <t>-2,83; 2,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,33</t>
+          <t>-1,36; 1,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,42</t>
+          <t>-1,22; 1,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,37</t>
+          <t>-1,37; 1,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 69,56</t>
+          <t>-49,75; 76,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,07; 52,99</t>
+          <t>-55,19; 56,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 62,49</t>
+          <t>-48,12; 77,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 85,92</t>
+          <t>-40,31; 85,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 110,13</t>
+          <t>-31,86; 98,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 79,03</t>
+          <t>-55,83; 77,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 47,86</t>
+          <t>-33,99; 47,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 53,77</t>
+          <t>-31,93; 55,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 51,13</t>
+          <t>-34,04; 62,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,93</t>
+          <t>-4,53; 1,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,95</t>
+          <t>-4,5; 0,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 5,16</t>
+          <t>-2,88; 5,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; -0,03</t>
+          <t>-4,63; 0,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,36</t>
+          <t>-4,68; 0,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,32</t>
+          <t>-4,37; 0,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,2</t>
+          <t>-3,69; -0,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -0,03</t>
+          <t>-3,61; 0,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,25</t>
+          <t>-3,02; 1,26</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-79,35; 68,44</t>
+          <t>-78,48; 64,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,9; 69,01</t>
+          <t>-79,95; 56,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 250,48</t>
+          <t>-65,81; 256,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 1,92</t>
+          <t>-75,16; 12,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-71,62; 17,18</t>
+          <t>-73,47; 22,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,26; 12,46</t>
+          <t>-67,47; 12,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,26; -2,49</t>
+          <t>-68,18; -2,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-67,83; 0,34</t>
+          <t>-66,91; 3,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 41,55</t>
+          <t>-55,8; 46,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,15</t>
+          <t>1,94; 11,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 5,49</t>
+          <t>-2,38; 5,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 7,69</t>
+          <t>-4,71; 7,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,77</t>
+          <t>-0,63; 2,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,51</t>
+          <t>-0,8; 2,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,63</t>
+          <t>-1,39; 2,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,1</t>
+          <t>0,57; 4,05</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,59</t>
+          <t>-0,55; 2,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,56</t>
+          <t>-1,5; 2,59</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>27,6; 398,25</t>
+          <t>25,92; 410,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 188,02</t>
+          <t>-39,37; 189,76</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-82,46; 258,6</t>
+          <t>-81,52; 243,44</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 112,04</t>
+          <t>-16,27; 118,95</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 103,67</t>
+          <t>-21,54; 111,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 109,02</t>
+          <t>-39,93; 100,53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,4; 150,13</t>
+          <t>13,11; 141,31</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 94,81</t>
+          <t>-14,18; 91,24</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 85,86</t>
+          <t>-39,38; 91,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,92</t>
+          <t>-1,2; 0,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,47</t>
+          <t>-1,54; 0,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,87</t>
+          <t>-1,53; 0,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,15</t>
+          <t>-0,84; 1,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,09</t>
+          <t>-0,85; 1,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,44</t>
+          <t>-0,75; 1,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,72</t>
+          <t>-0,71; 0,7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,5</t>
+          <t>-0,9; 0,47</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,8</t>
+          <t>-0,75; 0,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 31,42</t>
+          <t>-29,05; 28,02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 16,7</t>
+          <t>-38,35; 12,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 30,09</t>
+          <t>-38,24; 27,48</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 39,9</t>
+          <t>-21,15; 34,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 36,78</t>
+          <t>-22,53; 35,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 48,97</t>
+          <t>-17,96; 47,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 22,8</t>
+          <t>-18,75; 23,44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 15,76</t>
+          <t>-23,62; 15,36</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 25,65</t>
+          <t>-19,54; 24,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,96</t>
+          <t>-2,15; 3,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,28</t>
+          <t>-4,0; 0,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,32</t>
+          <t>-1,78; 3,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,45</t>
+          <t>1,16; 7,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,61</t>
+          <t>-0,48; 4,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,28</t>
+          <t>2,02; 6,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,03</t>
+          <t>-0,17; 4,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,66</t>
+          <t>-1,86; 1,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,29</t>
+          <t>0,41; 4,14</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>315,44%</t>
+          <t>288,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105,19%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,21; 157,57</t>
+          <t>-53,58; 228,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-88,77; 32,02</t>
+          <t>-87,27; 54,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 214,03</t>
+          <t>-38,28; 177,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 1170,11</t>
+          <t>12,0; 1286,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 853,55</t>
+          <t>-40,83; 951,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,83; 1503,44</t>
+          <t>52,48; 1669,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 250,23</t>
+          <t>-9,64; 272,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,05; 110,74</t>
+          <t>-58,46; 106,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,46; 269,19</t>
+          <t>11,25; 262,19</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -0,0</t>
+          <t>-5,18; -0,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,97</t>
+          <t>-3,36; 2,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,09</t>
+          <t>-3,62; 1,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -0,28</t>
+          <t>-5,75; -0,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,37</t>
+          <t>-4,56; 1,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,58</t>
+          <t>-3,76; 2,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,79</t>
+          <t>-4,48; -0,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,21</t>
+          <t>-3,2; 0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,64</t>
+          <t>-2,8; 1,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-11,93%</t>
+          <t>-16,22%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,5%</t>
+          <t>-11,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-10,3%</t>
+          <t>-14,89%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-90,26; 5,61</t>
+          <t>-93,15; 10,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 156,76</t>
+          <t>-64,07; 153,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 108,39</t>
+          <t>-67,24; 103,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,81; 2,32</t>
+          <t>-86,78; -1,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,76; 64,74</t>
+          <t>-73,38; 36,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,92; 88,98</t>
+          <t>-56,53; 79,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,71; -22,59</t>
+          <t>-81,27; -26,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,97; 40,69</t>
+          <t>-59,36; 34,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,1; 58,46</t>
+          <t>-52,11; 43,16</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>0,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,12</t>
+          <t>-3,53; 1,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,13</t>
+          <t>-3,36; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,76</t>
+          <t>-2,76; 2,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 3,79</t>
+          <t>-2,59; 3,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,46</t>
+          <t>-2,25; 6,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,94</t>
+          <t>-2,37; 3,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,2</t>
+          <t>-2,66; 1,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,9</t>
+          <t>-2,53; 1,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,87</t>
+          <t>-2,04; 2,27</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-45,28%</t>
+          <t>-6,74%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-33,5%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,32; 39,78</t>
+          <t>-63,85; 62,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,69; 75,38</t>
+          <t>-61,33; 64,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,46; 25,91</t>
+          <t>-54,29; 101,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,23; —</t>
+          <t>-69,7; 630,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,39; —</t>
+          <t>-78,68; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 580,92</t>
+          <t>-68,48; 500,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,58; 55,86</t>
+          <t>-56,89; 63,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 72,68</t>
+          <t>-53,93; 81,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,47; 25,47</t>
+          <t>-44,97; 90,91</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,58</t>
+          <t>-1,72; 1,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,12</t>
+          <t>-2,05; 1,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,47</t>
+          <t>-1,47; 2,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,33</t>
+          <t>-1,71; 2,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,59</t>
+          <t>-1,63; 2,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,37</t>
+          <t>-0,72; 3,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,27</t>
+          <t>-1,26; 1,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,43</t>
+          <t>-1,24; 1,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,65</t>
+          <t>-0,44; 2,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-7,24%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,75; 76,86</t>
+          <t>-47,95; 79,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 56,44</t>
+          <t>-53,83; 61,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 77,4</t>
+          <t>-40,13; 102,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 85,45</t>
+          <t>-36,22; 103,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 98,87</t>
+          <t>-35,25; 96,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,83; 77,73</t>
+          <t>-17,43; 129,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 47,12</t>
+          <t>-31,75; 53,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 55,57</t>
+          <t>-33,04; 47,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,04; 62,32</t>
+          <t>-11,94; 84,14</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-1,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,1</t>
+          <t>-4,26; 1,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,83</t>
+          <t>-4,51; 0,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 5,44</t>
+          <t>-3,7; 3,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,09</t>
+          <t>-4,49; 0,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 0,52</t>
+          <t>-4,23; 0,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,31</t>
+          <t>-3,68; 0,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,1</t>
+          <t>-3,66; -0,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,04</t>
+          <t>-3,47; 0,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,26</t>
+          <t>-3,01; 0,64</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>-18,41%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-37,76%</t>
+          <t>-30,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,42%</t>
+          <t>-27,14%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-78,48; 64,78</t>
+          <t>-77,36; 76,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,95; 56,14</t>
+          <t>-78,41; 64,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 256,39</t>
+          <t>-70,13; 180,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,16; 12,03</t>
+          <t>-72,74; 13,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-73,47; 22,4</t>
+          <t>-69,74; 31,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 12,93</t>
+          <t>-58,48; 43,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,18; -2,02</t>
+          <t>-67,23; -2,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 3,15</t>
+          <t>-64,92; 9,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 46,16</t>
+          <t>-58,42; 22,69</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,96</t>
+          <t>2,26; 12,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,74</t>
+          <t>-2,62; 5,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 7,45</t>
+          <t>-4,23; 6,31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,79</t>
+          <t>-0,61; 2,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,65</t>
+          <t>-0,81; 2,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,49</t>
+          <t>-1,3; 2,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,05</t>
+          <t>0,54; 4,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,55</t>
+          <t>-0,55; 2,76</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,59</t>
+          <t>-1,42; 2,29</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>-4,19%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>25,92; 410,22</t>
+          <t>25,91; 418,59</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 189,76</t>
+          <t>-42,92; 210,78</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-81,52; 243,44</t>
+          <t>-73,43; 241,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 118,95</t>
+          <t>-16,07; 119,31</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 111,49</t>
+          <t>-22,06; 117,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 100,53</t>
+          <t>-36,85; 99,88</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,11; 141,31</t>
+          <t>12,08; 149,48</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 91,24</t>
+          <t>-15,34; 104,42</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 91,5</t>
+          <t>-35,8; 82,18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,8</t>
+          <t>-1,12; 0,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,33</t>
+          <t>-1,63; 0,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,82</t>
+          <t>-1,18; 0,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,05</t>
+          <t>-0,79; 1,12</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,11</t>
+          <t>-0,83; 1,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,39</t>
+          <t>-0,1; 1,75</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,7</t>
+          <t>-0,69; 0,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,47</t>
+          <t>-0,85; 0,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,79</t>
+          <t>-0,44; 0,98</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-8,72%</t>
+          <t>-1,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 28,02</t>
+          <t>-28,6; 28,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 12,25</t>
+          <t>-40,83; 12,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 27,48</t>
+          <t>-29,57; 32,59</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 34,64</t>
+          <t>-20,76; 38,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 35,56</t>
+          <t>-21,89; 38,83</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 47,88</t>
+          <t>-3,0; 58,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 23,44</t>
+          <t>-18,15; 23,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 15,36</t>
+          <t>-22,55; 16,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 24,75</t>
+          <t>-11,67; 30,87</t>
         </is>
       </c>
     </row>
